--- a/data/cleaned/analysis_data.xlsx
+++ b/data/cleaned/analysis_data.xlsx
@@ -675,6 +675,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -735,7 +736,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>万人</t>
+          <t>万人次</t>
         </is>
       </c>
       <c r="C4" s="9" t="n">
